--- a/development/Orchestration/assets/Orchestration-1.2.0-XFZB-4.0.0-mapping.xlsx
+++ b/development/Orchestration/assets/Orchestration-1.2.0-XFZB-4.0.0-mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iataonline-my.sharepoint.com/personal/lambertc_iata_org/Documents/ONE Record/31 CXML mapping/Release 3.2.0 docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iataonline-my.sharepoint.com/personal/lambertc_iata_org/Documents/ONE Record/31 CXML mapping/Ochestration 1.2.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="8_{50F9FA9C-BD42-4B39-9627-8AF2541E7D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A59464EA-3AC0-4F85-B255-CBF09EF4A3B2}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="8_{50F9FA9C-BD42-4B39-9627-8AF2541E7D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CA38FB0-EC7F-4499-B043-6B87FD87B605}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{409C4CA4-810D-446E-B907-D73C99948B9B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="495">
   <si>
     <t>XFZB Message</t>
   </si>
@@ -1241,9 +1241,6 @@
     <t>Waybill#shipment -&gt; Shipment#goodsDescription</t>
   </si>
   <si>
-    <t>Waybill#waybillLineItems -&gt; WaybillLineItem#pieceReferences -&gt; Piece#volumetricWeigh -&gt; VolumetricWeight#conversionFactor</t>
-  </si>
-  <si>
     <t>Mapping remark</t>
   </si>
   <si>
@@ -1481,9 +1478,6 @@
     <t>ULD#tareWeight</t>
   </si>
   <si>
-    <t>ULD#slac</t>
-  </si>
-  <si>
     <t>ULD#uldTypeCode</t>
   </si>
   <si>
@@ -1521,6 +1515,15 @@
   </si>
   <si>
     <t>WaybillLineItem#rcp</t>
+  </si>
+  <si>
+    <t>ULD#inUnitComposition</t>
+  </si>
+  <si>
+    <t>UnitComposition#slac</t>
+  </si>
+  <si>
+    <t>WaybillLineItem#conversionFactor</t>
   </si>
 </sst>
 </file>
@@ -1590,7 +1593,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1609,13 +1612,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1636,8 +1648,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
@@ -1648,6 +1658,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1997,15 +2008,15 @@
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
       <c r="H2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2018,133 +2029,133 @@
       <c r="K2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="12" t="s">
-        <v>401</v>
+      <c r="L2" s="10" t="s">
+        <v>400</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="13"/>
+      <c r="L3" s="11"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="13"/>
+      <c r="L4" s="11"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="13" t="s">
-        <v>402</v>
+      <c r="L5" s="11" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="13" t="s">
-        <v>402</v>
+      <c r="L6" s="11" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="13" t="s">
-        <v>402</v>
+      <c r="L7" s="11" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>12</v>
       </c>
-      <c r="L8" s="13" t="s">
-        <v>402</v>
+      <c r="L8" s="11" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="L9" s="13" t="s">
-        <v>402</v>
+      <c r="L9" s="11" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="13" t="s">
-        <v>402</v>
+      <c r="L10" s="11" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>15</v>
       </c>
-      <c r="L11" s="13" t="s">
-        <v>402</v>
+      <c r="L11" s="11" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L12" s="13"/>
+      <c r="L12" s="11"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C13" s="1"/>
       <c r="D13" t="s">
         <v>17</v>
       </c>
-      <c r="L13" s="13" t="s">
-        <v>403</v>
+      <c r="L13" s="11" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L14" s="13"/>
+      <c r="L14" s="11"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L15" s="13"/>
+      <c r="L15" s="11"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>17</v>
       </c>
-      <c r="L16" s="13" t="s">
-        <v>404</v>
+      <c r="L16" s="11" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="13"/>
+      <c r="L17" s="11"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L18" s="13"/>
+      <c r="L18" s="11"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L19" s="13"/>
+      <c r="L19" s="11"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
@@ -2162,8 +2173,8 @@
       <c r="K20" t="s">
         <v>26</v>
       </c>
-      <c r="L20" s="13" t="s">
-        <v>406</v>
+      <c r="L20" s="11" t="s">
+        <v>405</v>
       </c>
       <c r="M20" t="s">
         <v>27</v>
@@ -2173,7 +2184,7 @@
       <c r="C21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L21" s="13"/>
+      <c r="L21" s="11"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
@@ -2188,7 +2199,7 @@
       <c r="J22" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L22" s="13"/>
+      <c r="L22" s="11"/>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D23" t="s">
@@ -2203,19 +2214,19 @@
       <c r="J23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L23" s="13"/>
+      <c r="L23" s="11"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C24" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L24" s="13"/>
+      <c r="L24" s="11"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L25" s="13"/>
+      <c r="L25" s="11"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D26" t="s">
@@ -2230,7 +2241,7 @@
       <c r="J26" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L26" s="13"/>
+      <c r="L26" s="11"/>
       <c r="M26" t="s">
         <v>39</v>
       </c>
@@ -2239,13 +2250,13 @@
       <c r="C27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L27" s="13"/>
+      <c r="L27" s="11"/>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C28" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L28" s="13"/>
+      <c r="L28" s="11"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D29" t="s">
@@ -2260,7 +2271,7 @@
       <c r="J29" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L29" s="13"/>
+      <c r="L29" s="11"/>
       <c r="M29" t="s">
         <v>44</v>
       </c>
@@ -2278,7 +2289,7 @@
       <c r="J30" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L30" s="13"/>
+      <c r="L30" s="11"/>
       <c r="M30" t="s">
         <v>46</v>
       </c>
@@ -2287,7 +2298,7 @@
       <c r="D31" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L31" s="13"/>
+      <c r="L31" s="11"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="E32" t="s">
@@ -2302,7 +2313,7 @@
       <c r="J32" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L32" s="13"/>
+      <c r="L32" s="11"/>
       <c r="M32" t="s">
         <v>49</v>
       </c>
@@ -2311,26 +2322,26 @@
       <c r="D33" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L33" s="13"/>
+      <c r="L33" s="11"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C34" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D34" s="1"/>
-      <c r="L34" s="13"/>
+      <c r="L34" s="11"/>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L35" s="13"/>
+      <c r="L35" s="11"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="L36" s="13"/>
+      <c r="L36" s="11"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
@@ -2345,14 +2356,14 @@
       <c r="J37" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L37" s="13" t="s">
+      <c r="L37" s="11" t="s">
         <v>57</v>
       </c>
       <c r="M37" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N37" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.25">
@@ -2368,21 +2379,21 @@
       <c r="J38" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L38" s="13" t="s">
+      <c r="L38" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="M38" t="s">
         <v>410</v>
       </c>
-      <c r="M38" t="s">
-        <v>411</v>
-      </c>
       <c r="N38" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C39" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="L39" s="13"/>
+      <c r="L39" s="11"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D40" t="s">
@@ -2397,7 +2408,7 @@
       <c r="J40" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L40" s="13" t="s">
+      <c r="L40" s="11" t="s">
         <v>64</v>
       </c>
       <c r="M40" t="s">
@@ -2408,13 +2419,13 @@
       <c r="C41" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="L41" s="13"/>
+      <c r="L41" s="11"/>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C42" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="L42" s="13"/>
+      <c r="L42" s="11"/>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D43" t="s">
@@ -2429,14 +2440,14 @@
       <c r="J43" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L43" s="13" t="s">
+      <c r="L43" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="M43" s="11" t="s">
+      <c r="M43" t="s">
+        <v>411</v>
+      </c>
+      <c r="N43" t="s">
         <v>412</v>
-      </c>
-      <c r="N43" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
@@ -2452,27 +2463,27 @@
       <c r="J44" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L44" s="13" t="s">
+      <c r="L44" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="M44" s="11" t="s">
-        <v>412</v>
+      <c r="M44" t="s">
+        <v>411</v>
       </c>
       <c r="N44" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C45" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="L45" s="13"/>
+      <c r="L45" s="11"/>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C46" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L46" s="13"/>
+      <c r="L46" s="11"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D47" t="s">
@@ -2487,14 +2498,14 @@
       <c r="J47" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L47" s="13" t="s">
+      <c r="L47" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="M47" s="11" t="s">
-        <v>415</v>
+      <c r="M47" t="s">
+        <v>414</v>
       </c>
       <c r="N47" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.25">
@@ -2510,27 +2521,27 @@
       <c r="J48" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L48" s="13" t="s">
+      <c r="L48" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="M48" s="11" t="s">
-        <v>415</v>
+      <c r="M48" t="s">
+        <v>414</v>
       </c>
       <c r="N48" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="49" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C49" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L49" s="13"/>
+      <c r="L49" s="11"/>
     </row>
     <row r="50" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C50" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="L50" s="13"/>
+      <c r="L50" s="11"/>
     </row>
     <row r="51" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D51" t="s">
@@ -2545,7 +2556,7 @@
       <c r="J51" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L51" s="13"/>
+      <c r="L51" s="11"/>
     </row>
     <row r="52" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D52" t="s">
@@ -2560,7 +2571,7 @@
       <c r="J52" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L52" s="13"/>
+      <c r="L52" s="11"/>
     </row>
     <row r="53" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D53" t="s">
@@ -2575,7 +2586,7 @@
       <c r="J53" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L53" s="13"/>
+      <c r="L53" s="11"/>
     </row>
     <row r="54" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D54" t="s">
@@ -2590,7 +2601,7 @@
       <c r="J54" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L54" s="13" t="s">
+      <c r="L54" s="11" t="s">
         <v>83</v>
       </c>
       <c r="M54" t="s">
@@ -2610,7 +2621,7 @@
       <c r="J55" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L55" s="13"/>
+      <c r="L55" s="11"/>
       <c r="M55" t="s">
         <v>82</v>
       </c>
@@ -2628,7 +2639,7 @@
       <c r="J56" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L56" s="13" t="s">
+      <c r="L56" s="11" t="s">
         <v>83</v>
       </c>
       <c r="M56" t="s">
@@ -2648,7 +2659,7 @@
       <c r="J57" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L57" s="13"/>
+      <c r="L57" s="11"/>
       <c r="M57" t="s">
         <v>88</v>
       </c>
@@ -2666,17 +2677,17 @@
       <c r="J58" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L58" s="13" t="s">
+      <c r="L58" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="M58" s="11" t="s">
-        <v>408</v>
+      <c r="M58" t="s">
+        <v>407</v>
       </c>
       <c r="N58" t="s">
+        <v>415</v>
+      </c>
+      <c r="O58" t="s">
         <v>416</v>
-      </c>
-      <c r="O58" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="59" spans="3:15" x14ac:dyDescent="0.25">
@@ -2692,15 +2703,15 @@
       <c r="J59" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L59" s="13"/>
-      <c r="M59" s="11" t="s">
-        <v>408</v>
+      <c r="L59" s="11"/>
+      <c r="M59" t="s">
+        <v>407</v>
       </c>
       <c r="N59" t="s">
+        <v>415</v>
+      </c>
+      <c r="O59" t="s">
         <v>416</v>
-      </c>
-      <c r="O59" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="60" spans="3:15" x14ac:dyDescent="0.25">
@@ -2716,7 +2727,7 @@
       <c r="J60" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L60" s="13"/>
+      <c r="L60" s="11"/>
       <c r="M60" t="s">
         <v>97</v>
       </c>
@@ -2734,7 +2745,7 @@
       <c r="J61" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L61" s="13"/>
+      <c r="L61" s="11"/>
       <c r="M61" t="s">
         <v>100</v>
       </c>
@@ -2752,7 +2763,7 @@
       <c r="J62" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L62" s="13"/>
+      <c r="L62" s="11"/>
       <c r="M62" t="s">
         <v>103</v>
       </c>
@@ -2770,7 +2781,7 @@
       <c r="J63" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L63" s="13"/>
+      <c r="L63" s="11"/>
       <c r="M63" t="s">
         <v>106</v>
       </c>
@@ -2788,7 +2799,7 @@
       <c r="J64" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L64" s="13"/>
+      <c r="L64" s="11"/>
       <c r="M64" t="s">
         <v>109</v>
       </c>
@@ -2806,7 +2817,7 @@
       <c r="J65" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L65" s="13"/>
+      <c r="L65" s="11"/>
       <c r="M65" s="7" t="s">
         <v>112</v>
       </c>
@@ -2824,7 +2835,7 @@
       <c r="J66" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L66" s="13"/>
+      <c r="L66" s="11"/>
       <c r="M66" s="7" t="s">
         <v>115</v>
       </c>
@@ -2843,7 +2854,7 @@
       <c r="J67" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L67" s="13"/>
+      <c r="L67" s="11"/>
       <c r="M67" t="s">
         <v>118</v>
       </c>
@@ -2861,7 +2872,7 @@
       <c r="J68" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L68" s="13"/>
+      <c r="L68" s="11"/>
       <c r="M68" t="s">
         <v>121</v>
       </c>
@@ -2879,7 +2890,7 @@
       <c r="J69" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L69" s="13"/>
+      <c r="L69" s="11"/>
       <c r="M69" t="s">
         <v>56</v>
       </c>
@@ -2897,7 +2908,7 @@
       <c r="J70" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L70" s="13"/>
+      <c r="L70" s="11"/>
       <c r="M70" t="s">
         <v>126</v>
       </c>
@@ -2915,7 +2926,7 @@
       <c r="J71" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L71" s="13"/>
+      <c r="L71" s="11"/>
       <c r="M71" t="s">
         <v>397</v>
       </c>
@@ -2933,7 +2944,7 @@
       <c r="J72" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L72" s="13"/>
+      <c r="L72" s="11"/>
       <c r="M72" t="s">
         <v>398</v>
       </c>
@@ -2951,7 +2962,7 @@
       <c r="J73" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L73" s="13"/>
+      <c r="L73" s="11"/>
       <c r="M73" t="s">
         <v>60</v>
       </c>
@@ -2969,7 +2980,7 @@
       <c r="J74" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L74" s="13"/>
+      <c r="L74" s="11"/>
       <c r="M74" t="s">
         <v>399</v>
       </c>
@@ -2980,7 +2991,7 @@
       </c>
       <c r="H75" s="5"/>
       <c r="K75" s="9"/>
-      <c r="L75" s="13"/>
+      <c r="L75" s="11"/>
     </row>
     <row r="76" spans="4:23" x14ac:dyDescent="0.25">
       <c r="D76" s="1" t="s">
@@ -2992,7 +3003,7 @@
       <c r="J76" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L76" s="13"/>
+      <c r="L76" s="11"/>
       <c r="M76" t="s">
         <v>137</v>
       </c>
@@ -3010,7 +3021,7 @@
       <c r="J77" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L77" s="13"/>
+      <c r="L77" s="11"/>
     </row>
     <row r="78" spans="4:23" x14ac:dyDescent="0.25">
       <c r="E78" t="s">
@@ -3025,7 +3036,7 @@
       <c r="J78" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L78" s="13"/>
+      <c r="L78" s="11"/>
     </row>
     <row r="79" spans="4:23" x14ac:dyDescent="0.25">
       <c r="E79" t="s">
@@ -3040,7 +3051,7 @@
       <c r="J79" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L79" s="13"/>
+      <c r="L79" s="11"/>
     </row>
     <row r="80" spans="4:23" x14ac:dyDescent="0.25">
       <c r="E80" t="s">
@@ -3055,7 +3066,7 @@
       <c r="J80" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L80" s="13"/>
+      <c r="L80" s="11"/>
     </row>
     <row r="81" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E81" s="1" t="s">
@@ -3067,7 +3078,7 @@
       <c r="J81" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L81" s="13"/>
+      <c r="L81" s="11"/>
     </row>
     <row r="82" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F82" t="s">
@@ -3082,7 +3093,7 @@
       <c r="J82" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L82" s="13"/>
+      <c r="L82" s="11"/>
     </row>
     <row r="83" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F83" t="s">
@@ -3097,7 +3108,7 @@
       <c r="J83" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L83" s="13"/>
+      <c r="L83" s="11"/>
     </row>
     <row r="84" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F84" t="s">
@@ -3112,7 +3123,7 @@
       <c r="J84" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L84" s="13"/>
+      <c r="L84" s="11"/>
     </row>
     <row r="85" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F85" t="s">
@@ -3127,7 +3138,7 @@
       <c r="J85" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L85" s="13"/>
+      <c r="L85" s="11"/>
     </row>
     <row r="86" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F86" t="s">
@@ -3142,7 +3153,7 @@
       <c r="J86" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L86" s="13"/>
+      <c r="L86" s="11"/>
     </row>
     <row r="87" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F87" t="s">
@@ -3157,7 +3168,7 @@
       <c r="J87" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L87" s="13"/>
+      <c r="L87" s="11"/>
     </row>
     <row r="88" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F88" t="s">
@@ -3172,7 +3183,7 @@
       <c r="J88" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L88" s="13"/>
+      <c r="L88" s="11"/>
     </row>
     <row r="89" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F89" t="s">
@@ -3187,7 +3198,7 @@
       <c r="J89" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L89" s="13"/>
+      <c r="L89" s="11"/>
     </row>
     <row r="90" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F90" t="s">
@@ -3202,14 +3213,14 @@
       <c r="J90" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L90" s="13"/>
+      <c r="L90" s="11"/>
     </row>
     <row r="91" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E91" s="1" t="s">
         <v>163</v>
       </c>
       <c r="J91" s="6"/>
-      <c r="L91" s="13"/>
+      <c r="L91" s="11"/>
     </row>
     <row r="92" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E92" s="1" t="s">
@@ -3221,7 +3232,7 @@
       <c r="J92" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L92" s="13"/>
+      <c r="L92" s="11"/>
     </row>
     <row r="93" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F93" t="s">
@@ -3236,7 +3247,7 @@
       <c r="J93" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L93" s="13"/>
+      <c r="L93" s="11"/>
     </row>
     <row r="94" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F94" t="s">
@@ -3251,7 +3262,7 @@
       <c r="J94" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L94" s="13"/>
+      <c r="L94" s="11"/>
     </row>
     <row r="95" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F95" s="1" t="s">
@@ -3263,7 +3274,7 @@
       <c r="J95" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L95" s="13"/>
+      <c r="L95" s="11"/>
     </row>
     <row r="96" spans="5:12" x14ac:dyDescent="0.25">
       <c r="G96" t="s">
@@ -3278,14 +3289,14 @@
       <c r="J96" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L96" s="13"/>
+      <c r="L96" s="11"/>
     </row>
     <row r="97" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F97" s="1" t="s">
         <v>172</v>
       </c>
       <c r="J97" s="6"/>
-      <c r="L97" s="13"/>
+      <c r="L97" s="11"/>
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F98" s="1" t="s">
@@ -3297,7 +3308,7 @@
       <c r="J98" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L98" s="13"/>
+      <c r="L98" s="11"/>
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.25">
       <c r="G99" t="s">
@@ -3312,14 +3323,14 @@
       <c r="J99" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L99" s="13"/>
+      <c r="L99" s="11"/>
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F100" s="1" t="s">
         <v>175</v>
       </c>
       <c r="J100" s="6"/>
-      <c r="L100" s="13"/>
+      <c r="L100" s="11"/>
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F101" s="1" t="s">
@@ -3331,7 +3342,7 @@
       <c r="J101" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L101" s="13"/>
+      <c r="L101" s="11"/>
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F102" s="1"/>
@@ -3347,14 +3358,14 @@
       <c r="J102" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L102" s="13"/>
+      <c r="L102" s="11"/>
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F103" s="1" t="s">
         <v>179</v>
       </c>
       <c r="J103" s="6"/>
-      <c r="L103" s="13"/>
+      <c r="L103" s="11"/>
     </row>
     <row r="104" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F104" s="1" t="s">
@@ -3366,7 +3377,7 @@
       <c r="J104" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L104" s="13"/>
+      <c r="L104" s="11"/>
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.25">
       <c r="G105" t="s">
@@ -3381,27 +3392,27 @@
       <c r="J105" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L105" s="13"/>
+      <c r="L105" s="11"/>
     </row>
     <row r="106" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F106" s="1" t="s">
         <v>182</v>
       </c>
       <c r="J106" s="6"/>
-      <c r="L106" s="13"/>
+      <c r="L106" s="11"/>
     </row>
     <row r="107" spans="4:13" x14ac:dyDescent="0.25">
       <c r="E107" s="1" t="s">
         <v>183</v>
       </c>
       <c r="J107" s="6"/>
-      <c r="L107" s="13"/>
+      <c r="L107" s="11"/>
     </row>
     <row r="108" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D108" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="L108" s="13"/>
+      <c r="L108" s="11"/>
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D109" s="1" t="s">
@@ -3413,7 +3424,7 @@
       <c r="J109" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L109" s="13"/>
+      <c r="L109" s="11"/>
       <c r="M109" t="s">
         <v>137</v>
       </c>
@@ -3431,7 +3442,7 @@
       <c r="J110" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L110" s="13"/>
+      <c r="L110" s="11"/>
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.25">
       <c r="E111" t="s">
@@ -3446,7 +3457,7 @@
       <c r="J111" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L111" s="13"/>
+      <c r="L111" s="11"/>
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.25">
       <c r="E112" t="s">
@@ -3461,7 +3472,7 @@
       <c r="J112" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L112" s="13"/>
+      <c r="L112" s="11"/>
     </row>
     <row r="113" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E113" t="s">
@@ -3476,7 +3487,7 @@
       <c r="J113" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L113" s="13"/>
+      <c r="L113" s="11"/>
     </row>
     <row r="114" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E114" s="1" t="s">
@@ -3488,7 +3499,7 @@
       <c r="J114" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L114" s="13"/>
+      <c r="L114" s="11"/>
     </row>
     <row r="115" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F115" t="s">
@@ -3503,7 +3514,7 @@
       <c r="J115" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L115" s="13"/>
+      <c r="L115" s="11"/>
     </row>
     <row r="116" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F116" t="s">
@@ -3518,7 +3529,7 @@
       <c r="J116" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L116" s="13"/>
+      <c r="L116" s="11"/>
     </row>
     <row r="117" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F117" t="s">
@@ -3533,7 +3544,7 @@
       <c r="J117" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L117" s="13"/>
+      <c r="L117" s="11"/>
     </row>
     <row r="118" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F118" t="s">
@@ -3548,7 +3559,7 @@
       <c r="J118" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L118" s="13"/>
+      <c r="L118" s="11"/>
     </row>
     <row r="119" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F119" t="s">
@@ -3563,7 +3574,7 @@
       <c r="J119" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L119" s="13"/>
+      <c r="L119" s="11"/>
     </row>
     <row r="120" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F120" t="s">
@@ -3578,7 +3589,7 @@
       <c r="J120" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L120" s="13"/>
+      <c r="L120" s="11"/>
     </row>
     <row r="121" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F121" t="s">
@@ -3593,7 +3604,7 @@
       <c r="J121" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L121" s="13"/>
+      <c r="L121" s="11"/>
     </row>
     <row r="122" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F122" t="s">
@@ -3608,7 +3619,7 @@
       <c r="J122" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L122" s="13"/>
+      <c r="L122" s="11"/>
     </row>
     <row r="123" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F123" t="s">
@@ -3623,14 +3634,14 @@
       <c r="J123" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L123" s="13"/>
+      <c r="L123" s="11"/>
     </row>
     <row r="124" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E124" s="1" t="s">
         <v>163</v>
       </c>
       <c r="J124" s="6"/>
-      <c r="L124" s="13"/>
+      <c r="L124" s="11"/>
     </row>
     <row r="125" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E125" s="1" t="s">
@@ -3642,7 +3653,7 @@
       <c r="J125" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L125" s="13"/>
+      <c r="L125" s="11"/>
     </row>
     <row r="126" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F126" t="s">
@@ -3657,7 +3668,7 @@
       <c r="J126" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L126" s="13"/>
+      <c r="L126" s="11"/>
     </row>
     <row r="127" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F127" t="s">
@@ -3672,7 +3683,7 @@
       <c r="J127" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L127" s="13"/>
+      <c r="L127" s="11"/>
     </row>
     <row r="128" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F128" s="1" t="s">
@@ -3684,7 +3695,7 @@
       <c r="J128" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L128" s="13"/>
+      <c r="L128" s="11"/>
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.25">
       <c r="G129" t="s">
@@ -3699,14 +3710,14 @@
       <c r="J129" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L129" s="13"/>
+      <c r="L129" s="11"/>
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F130" s="1" t="s">
         <v>172</v>
       </c>
       <c r="J130" s="6"/>
-      <c r="L130" s="13"/>
+      <c r="L130" s="11"/>
     </row>
     <row r="131" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F131" s="1" t="s">
@@ -3718,7 +3729,7 @@
       <c r="J131" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L131" s="13"/>
+      <c r="L131" s="11"/>
     </row>
     <row r="132" spans="4:13" x14ac:dyDescent="0.25">
       <c r="G132" t="s">
@@ -3733,14 +3744,14 @@
       <c r="J132" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L132" s="13"/>
+      <c r="L132" s="11"/>
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F133" s="1" t="s">
         <v>175</v>
       </c>
       <c r="J133" s="6"/>
-      <c r="L133" s="13"/>
+      <c r="L133" s="11"/>
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F134" s="1" t="s">
@@ -3752,7 +3763,7 @@
       <c r="J134" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L134" s="13"/>
+      <c r="L134" s="11"/>
     </row>
     <row r="135" spans="4:13" x14ac:dyDescent="0.25">
       <c r="G135" t="s">
@@ -3767,14 +3778,14 @@
       <c r="J135" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L135" s="13"/>
+      <c r="L135" s="11"/>
     </row>
     <row r="136" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F136" s="1" t="s">
         <v>179</v>
       </c>
       <c r="J136" s="6"/>
-      <c r="L136" s="13"/>
+      <c r="L136" s="11"/>
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F137" s="1" t="s">
@@ -3786,7 +3797,7 @@
       <c r="J137" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L137" s="13"/>
+      <c r="L137" s="11"/>
     </row>
     <row r="138" spans="4:13" x14ac:dyDescent="0.25">
       <c r="G138" t="s">
@@ -3801,27 +3812,27 @@
       <c r="J138" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L138" s="13"/>
+      <c r="L138" s="11"/>
     </row>
     <row r="139" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F139" s="1" t="s">
         <v>182</v>
       </c>
       <c r="J139" s="6"/>
-      <c r="L139" s="13"/>
+      <c r="L139" s="11"/>
     </row>
     <row r="140" spans="4:13" x14ac:dyDescent="0.25">
       <c r="E140" s="1" t="s">
         <v>183</v>
       </c>
       <c r="J140" s="6"/>
-      <c r="L140" s="13"/>
+      <c r="L140" s="11"/>
     </row>
     <row r="141" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D141" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="L141" s="13"/>
+      <c r="L141" s="11"/>
     </row>
     <row r="142" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D142" s="1" t="s">
@@ -3833,7 +3844,7 @@
       <c r="J142" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L142" s="13"/>
+      <c r="L142" s="11"/>
       <c r="M142" t="s">
         <v>137</v>
       </c>
@@ -3851,7 +3862,7 @@
       <c r="J143" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L143" s="13"/>
+      <c r="L143" s="11"/>
     </row>
     <row r="144" spans="4:13" x14ac:dyDescent="0.25">
       <c r="E144" t="s">
@@ -3866,7 +3877,7 @@
       <c r="J144" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L144" s="13"/>
+      <c r="L144" s="11"/>
     </row>
     <row r="145" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E145" t="s">
@@ -3881,7 +3892,7 @@
       <c r="J145" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L145" s="13"/>
+      <c r="L145" s="11"/>
     </row>
     <row r="146" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E146" t="s">
@@ -3896,13 +3907,13 @@
       <c r="J146" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L146" s="13"/>
+      <c r="L146" s="11"/>
     </row>
     <row r="147" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E147" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="L147" s="13"/>
+      <c r="L147" s="11"/>
     </row>
     <row r="148" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F148" t="s">
@@ -3917,7 +3928,7 @@
       <c r="J148" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L148" s="13"/>
+      <c r="L148" s="11"/>
     </row>
     <row r="149" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F149" t="s">
@@ -3932,7 +3943,7 @@
       <c r="J149" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L149" s="13"/>
+      <c r="L149" s="11"/>
     </row>
     <row r="150" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F150" t="s">
@@ -3947,7 +3958,7 @@
       <c r="J150" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L150" s="13"/>
+      <c r="L150" s="11"/>
     </row>
     <row r="151" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F151" t="s">
@@ -3962,7 +3973,7 @@
       <c r="J151" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L151" s="13"/>
+      <c r="L151" s="11"/>
     </row>
     <row r="152" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F152" t="s">
@@ -3977,7 +3988,7 @@
       <c r="J152" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L152" s="13"/>
+      <c r="L152" s="11"/>
     </row>
     <row r="153" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F153" t="s">
@@ -3992,7 +4003,7 @@
       <c r="J153" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L153" s="13"/>
+      <c r="L153" s="11"/>
     </row>
     <row r="154" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F154" t="s">
@@ -4007,7 +4018,7 @@
       <c r="J154" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L154" s="13"/>
+      <c r="L154" s="11"/>
     </row>
     <row r="155" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F155" t="s">
@@ -4022,7 +4033,7 @@
       <c r="J155" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L155" s="13"/>
+      <c r="L155" s="11"/>
     </row>
     <row r="156" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F156" t="s">
@@ -4037,13 +4048,13 @@
       <c r="J156" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L156" s="13"/>
+      <c r="L156" s="11"/>
     </row>
     <row r="157" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E157" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L157" s="13"/>
+      <c r="L157" s="11"/>
     </row>
     <row r="158" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E158" s="1" t="s">
@@ -4055,7 +4066,7 @@
       <c r="J158" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L158" s="13"/>
+      <c r="L158" s="11"/>
     </row>
     <row r="159" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F159" t="s">
@@ -4070,7 +4081,7 @@
       <c r="J159" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L159" s="13"/>
+      <c r="L159" s="11"/>
     </row>
     <row r="160" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F160" t="s">
@@ -4085,7 +4096,7 @@
       <c r="J160" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L160" s="13"/>
+      <c r="L160" s="11"/>
     </row>
     <row r="161" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F161" s="1" t="s">
@@ -4097,7 +4108,7 @@
       <c r="J161" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L161" s="13"/>
+      <c r="L161" s="11"/>
     </row>
     <row r="162" spans="4:13" x14ac:dyDescent="0.25">
       <c r="G162" t="s">
@@ -4112,14 +4123,14 @@
       <c r="J162" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L162" s="13"/>
+      <c r="L162" s="11"/>
     </row>
     <row r="163" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F163" s="1" t="s">
         <v>172</v>
       </c>
       <c r="J163" s="6"/>
-      <c r="L163" s="13"/>
+      <c r="L163" s="11"/>
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F164" s="1" t="s">
@@ -4131,7 +4142,7 @@
       <c r="J164" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L164" s="13"/>
+      <c r="L164" s="11"/>
     </row>
     <row r="165" spans="4:13" x14ac:dyDescent="0.25">
       <c r="G165" t="s">
@@ -4146,14 +4157,14 @@
       <c r="J165" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L165" s="13"/>
+      <c r="L165" s="11"/>
     </row>
     <row r="166" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F166" s="1" t="s">
         <v>175</v>
       </c>
       <c r="J166" s="6"/>
-      <c r="L166" s="13"/>
+      <c r="L166" s="11"/>
     </row>
     <row r="167" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F167" s="1" t="s">
@@ -4165,7 +4176,7 @@
       <c r="J167" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L167" s="13"/>
+      <c r="L167" s="11"/>
     </row>
     <row r="168" spans="4:13" x14ac:dyDescent="0.25">
       <c r="G168" t="s">
@@ -4180,14 +4191,14 @@
       <c r="J168" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L168" s="13"/>
+      <c r="L168" s="11"/>
     </row>
     <row r="169" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F169" s="1" t="s">
         <v>179</v>
       </c>
       <c r="J169" s="6"/>
-      <c r="L169" s="13"/>
+      <c r="L169" s="11"/>
     </row>
     <row r="170" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F170" s="1" t="s">
@@ -4199,7 +4210,7 @@
       <c r="J170" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L170" s="13"/>
+      <c r="L170" s="11"/>
     </row>
     <row r="171" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F171" s="1"/>
@@ -4215,31 +4226,31 @@
       <c r="J171" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L171" s="13"/>
+      <c r="L171" s="11"/>
     </row>
     <row r="172" spans="4:13" x14ac:dyDescent="0.25">
       <c r="F172" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="L172" s="13"/>
+      <c r="L172" s="11"/>
     </row>
     <row r="173" spans="4:13" x14ac:dyDescent="0.25">
       <c r="E173" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="L173" s="13"/>
+      <c r="L173" s="11"/>
     </row>
     <row r="174" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D174" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="L174" s="13"/>
+      <c r="L174" s="11"/>
     </row>
     <row r="175" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D175" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="L175" s="13"/>
+      <c r="L175" s="11"/>
       <c r="M175" t="s">
         <v>137</v>
       </c>
@@ -4257,7 +4268,7 @@
       <c r="J176" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L176" s="13"/>
+      <c r="L176" s="11"/>
     </row>
     <row r="177" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E177" t="s">
@@ -4272,7 +4283,7 @@
       <c r="J177" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L177" s="13"/>
+      <c r="L177" s="11"/>
     </row>
     <row r="178" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E178" t="s">
@@ -4287,7 +4298,7 @@
       <c r="J178" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L178" s="13"/>
+      <c r="L178" s="11"/>
     </row>
     <row r="179" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E179" t="s">
@@ -4302,19 +4313,19 @@
       <c r="J179" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L179" s="13"/>
+      <c r="L179" s="11"/>
     </row>
     <row r="180" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E180" t="s">
         <v>205</v>
       </c>
-      <c r="L180" s="13"/>
+      <c r="L180" s="11"/>
     </row>
     <row r="181" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E181" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="L181" s="13"/>
+      <c r="L181" s="11"/>
     </row>
     <row r="182" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F182" t="s">
@@ -4329,7 +4340,7 @@
       <c r="J182" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L182" s="13"/>
+      <c r="L182" s="11"/>
     </row>
     <row r="183" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F183" t="s">
@@ -4344,7 +4355,7 @@
       <c r="J183" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L183" s="13"/>
+      <c r="L183" s="11"/>
     </row>
     <row r="184" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F184" t="s">
@@ -4359,7 +4370,7 @@
       <c r="J184" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L184" s="13"/>
+      <c r="L184" s="11"/>
     </row>
     <row r="185" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F185" t="s">
@@ -4374,7 +4385,7 @@
       <c r="J185" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L185" s="13"/>
+      <c r="L185" s="11"/>
     </row>
     <row r="186" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F186" t="s">
@@ -4389,7 +4400,7 @@
       <c r="J186" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L186" s="13"/>
+      <c r="L186" s="11"/>
     </row>
     <row r="187" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F187" t="s">
@@ -4404,7 +4415,7 @@
       <c r="J187" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L187" s="13"/>
+      <c r="L187" s="11"/>
     </row>
     <row r="188" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F188" t="s">
@@ -4419,7 +4430,7 @@
       <c r="J188" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L188" s="13"/>
+      <c r="L188" s="11"/>
     </row>
     <row r="189" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F189" t="s">
@@ -4434,7 +4445,7 @@
       <c r="J189" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L189" s="13"/>
+      <c r="L189" s="11"/>
     </row>
     <row r="190" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F190" t="s">
@@ -4449,13 +4460,13 @@
       <c r="J190" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L190" s="13"/>
+      <c r="L190" s="11"/>
     </row>
     <row r="191" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F191" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="L191" s="13"/>
+      <c r="L191" s="11"/>
     </row>
     <row r="192" spans="5:12" x14ac:dyDescent="0.25">
       <c r="G192" t="s">
@@ -4470,7 +4481,7 @@
       <c r="J192" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L192" s="13"/>
+      <c r="L192" s="11"/>
     </row>
     <row r="193" spans="5:12" x14ac:dyDescent="0.25">
       <c r="G193" t="s">
@@ -4485,7 +4496,7 @@
       <c r="J193" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L193" s="13"/>
+      <c r="L193" s="11"/>
     </row>
     <row r="194" spans="5:12" x14ac:dyDescent="0.25">
       <c r="G194" t="s">
@@ -4500,19 +4511,19 @@
       <c r="J194" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L194" s="13"/>
+      <c r="L194" s="11"/>
     </row>
     <row r="195" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F195" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L195" s="13"/>
+      <c r="L195" s="11"/>
     </row>
     <row r="196" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E196" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L196" s="13"/>
+      <c r="L196" s="11"/>
     </row>
     <row r="197" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E197" s="1" t="s">
@@ -4524,7 +4535,7 @@
       <c r="J197" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L197" s="13"/>
+      <c r="L197" s="11"/>
     </row>
     <row r="198" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F198" t="s">
@@ -4539,7 +4550,7 @@
       <c r="J198" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L198" s="13"/>
+      <c r="L198" s="11"/>
     </row>
     <row r="199" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F199" t="s">
@@ -4554,7 +4565,7 @@
       <c r="J199" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L199" s="13"/>
+      <c r="L199" s="11"/>
     </row>
     <row r="200" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F200" t="s">
@@ -4566,7 +4577,7 @@
       <c r="J200" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L200" s="13"/>
+      <c r="L200" s="11"/>
     </row>
     <row r="201" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F201" s="1"/>
@@ -4582,14 +4593,14 @@
       <c r="J201" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L201" s="13"/>
+      <c r="L201" s="11"/>
     </row>
     <row r="202" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F202" s="1" t="s">
         <v>172</v>
       </c>
       <c r="J202" s="6"/>
-      <c r="L202" s="13"/>
+      <c r="L202" s="11"/>
     </row>
     <row r="203" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F203" s="1" t="s">
@@ -4601,7 +4612,7 @@
       <c r="J203" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L203" s="13"/>
+      <c r="L203" s="11"/>
     </row>
     <row r="204" spans="5:12" x14ac:dyDescent="0.25">
       <c r="G204" t="s">
@@ -4616,14 +4627,14 @@
       <c r="J204" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L204" s="13"/>
+      <c r="L204" s="11"/>
     </row>
     <row r="205" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F205" s="1" t="s">
         <v>175</v>
       </c>
       <c r="J205" s="6"/>
-      <c r="L205" s="13"/>
+      <c r="L205" s="11"/>
     </row>
     <row r="206" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F206" s="1" t="s">
@@ -4635,7 +4646,7 @@
       <c r="J206" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L206" s="13"/>
+      <c r="L206" s="11"/>
     </row>
     <row r="207" spans="5:12" x14ac:dyDescent="0.25">
       <c r="G207" t="s">
@@ -4650,14 +4661,14 @@
       <c r="J207" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L207" s="13"/>
+      <c r="L207" s="11"/>
     </row>
     <row r="208" spans="5:12" x14ac:dyDescent="0.25">
       <c r="F208" s="1" t="s">
         <v>179</v>
       </c>
       <c r="J208" s="6"/>
-      <c r="L208" s="13"/>
+      <c r="L208" s="11"/>
     </row>
     <row r="209" spans="4:15" x14ac:dyDescent="0.25">
       <c r="F209" s="1" t="s">
@@ -4669,7 +4680,7 @@
       <c r="J209" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L209" s="13"/>
+      <c r="L209" s="11"/>
     </row>
     <row r="210" spans="4:15" x14ac:dyDescent="0.25">
       <c r="G210" t="s">
@@ -4684,37 +4695,37 @@
       <c r="J210" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L210" s="13"/>
+      <c r="L210" s="11"/>
     </row>
     <row r="211" spans="4:15" x14ac:dyDescent="0.25">
       <c r="F211" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="L211" s="13"/>
+      <c r="L211" s="11"/>
     </row>
     <row r="212" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E212" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="L212" s="13"/>
+      <c r="L212" s="11"/>
     </row>
     <row r="213" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D213" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="L213" s="13"/>
+      <c r="L213" s="11"/>
     </row>
     <row r="214" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D214" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="L214" s="13"/>
+      <c r="L214" s="11"/>
     </row>
     <row r="215" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E215" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="L215" s="13"/>
+      <c r="L215" s="11"/>
     </row>
     <row r="216" spans="4:15" x14ac:dyDescent="0.25">
       <c r="F216" t="s">
@@ -4729,34 +4740,34 @@
       <c r="J216" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L216" s="13"/>
+      <c r="L216" s="11"/>
       <c r="M216" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N216" t="s">
+        <v>417</v>
+      </c>
+      <c r="O216" t="s">
         <v>418</v>
-      </c>
-      <c r="O216" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="217" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E217" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="L217" s="13"/>
+      <c r="L217" s="11"/>
     </row>
     <row r="218" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D218" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="L218" s="13"/>
+      <c r="L218" s="11"/>
     </row>
     <row r="219" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D219" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="L219" s="13"/>
+      <c r="L219" s="11"/>
     </row>
     <row r="220" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E220" t="s">
@@ -4771,12 +4782,12 @@
       <c r="J220" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L220" s="13"/>
-      <c r="M220" s="11" t="s">
+      <c r="L220" s="11"/>
+      <c r="M220" t="s">
+        <v>411</v>
+      </c>
+      <c r="N220" t="s">
         <v>412</v>
-      </c>
-      <c r="N220" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="221" spans="4:15" x14ac:dyDescent="0.25">
@@ -4792,25 +4803,25 @@
       <c r="J221" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L221" s="13"/>
-      <c r="M221" s="11" t="s">
-        <v>412</v>
+      <c r="L221" s="11"/>
+      <c r="M221" t="s">
+        <v>411</v>
       </c>
       <c r="N221" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="222" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D222" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="L222" s="13"/>
+      <c r="L222" s="11"/>
     </row>
     <row r="223" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D223" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L223" s="13"/>
+      <c r="L223" s="11"/>
     </row>
     <row r="224" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E224" t="s">
@@ -4825,12 +4836,12 @@
       <c r="J224" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L224" s="13"/>
-      <c r="M224" s="11" t="s">
-        <v>415</v>
+      <c r="L224" s="11"/>
+      <c r="M224" t="s">
+        <v>414</v>
       </c>
       <c r="N224" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="225" spans="4:19" x14ac:dyDescent="0.25">
@@ -4846,25 +4857,25 @@
       <c r="J225" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L225" s="13"/>
-      <c r="M225" s="11" t="s">
-        <v>415</v>
+      <c r="L225" s="11"/>
+      <c r="M225" t="s">
+        <v>414</v>
       </c>
       <c r="N225" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="226" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D226" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L226" s="13"/>
+      <c r="L226" s="11"/>
     </row>
     <row r="227" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D227" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="L227" s="13"/>
+      <c r="L227" s="11"/>
     </row>
     <row r="228" spans="4:19" x14ac:dyDescent="0.25">
       <c r="E228" t="s">
@@ -4879,20 +4890,20 @@
       <c r="J228" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L228" s="14" t="s">
-        <v>432</v>
-      </c>
-      <c r="M228" s="11" t="s">
+      <c r="L228" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="M228" t="s">
+        <v>419</v>
+      </c>
+      <c r="N228" t="s">
         <v>420</v>
       </c>
-      <c r="N228" t="s">
+      <c r="O228" t="s">
         <v>421</v>
       </c>
-      <c r="O228" t="s">
+      <c r="P228" t="s">
         <v>422</v>
-      </c>
-      <c r="P228" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="229" spans="4:19" x14ac:dyDescent="0.25">
@@ -4908,20 +4919,20 @@
       <c r="J229" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L229" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="M229" s="11" t="s">
+      <c r="L229" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="M229" t="s">
+        <v>419</v>
+      </c>
+      <c r="N229" t="s">
         <v>420</v>
       </c>
-      <c r="N229" t="s">
+      <c r="O229" t="s">
         <v>421</v>
       </c>
-      <c r="O229" t="s">
-        <v>422</v>
-      </c>
       <c r="P229" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="230" spans="4:19" x14ac:dyDescent="0.25">
@@ -4937,7 +4948,7 @@
       <c r="J230" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L230" s="13"/>
+      <c r="L230" s="11"/>
       <c r="M230" t="s">
         <v>229</v>
       </c>
@@ -4955,18 +4966,18 @@
       <c r="J231" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L231" s="13"/>
-      <c r="M231" s="11" t="s">
+      <c r="L231" s="11"/>
+      <c r="M231" t="s">
+        <v>419</v>
+      </c>
+      <c r="N231" t="s">
         <v>420</v>
       </c>
-      <c r="N231" t="s">
+      <c r="O231" t="s">
         <v>421</v>
       </c>
-      <c r="O231" t="s">
-        <v>422</v>
-      </c>
       <c r="P231" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="232" spans="4:19" x14ac:dyDescent="0.25">
@@ -4982,22 +4993,22 @@
       <c r="J232" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L232" s="13"/>
-      <c r="M232" s="11" t="s">
+      <c r="L232" s="11"/>
+      <c r="M232" t="s">
+        <v>419</v>
+      </c>
+      <c r="N232" t="s">
         <v>420</v>
       </c>
-      <c r="N232" t="s">
-        <v>421</v>
-      </c>
       <c r="O232" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="233" spans="4:19" x14ac:dyDescent="0.25">
       <c r="E233" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="L233" s="13"/>
+      <c r="L233" s="11"/>
     </row>
     <row r="234" spans="4:19" x14ac:dyDescent="0.25">
       <c r="F234" t="s">
@@ -5012,58 +5023,58 @@
       <c r="J234" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L234" s="15" t="s">
+      <c r="L234" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="M234" t="s">
+        <v>419</v>
+      </c>
+      <c r="N234" t="s">
+        <v>420</v>
+      </c>
+      <c r="O234" t="s">
+        <v>421</v>
+      </c>
+      <c r="P234" t="s">
         <v>427</v>
       </c>
-      <c r="M234" s="11" t="s">
-        <v>420</v>
-      </c>
-      <c r="N234" t="s">
-        <v>421</v>
-      </c>
-      <c r="O234" t="s">
-        <v>422</v>
-      </c>
-      <c r="P234" t="s">
+      <c r="Q234" t="s">
         <v>428</v>
       </c>
-      <c r="Q234" t="s">
+      <c r="R234" t="s">
         <v>429</v>
       </c>
-      <c r="R234" t="s">
+      <c r="S234" t="s">
         <v>430</v>
-      </c>
-      <c r="S234" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="235" spans="4:19" x14ac:dyDescent="0.25">
       <c r="E235" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="L235" s="13"/>
+      <c r="L235" s="11"/>
     </row>
     <row r="236" spans="4:19" x14ac:dyDescent="0.25">
       <c r="E236" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="L236" s="14" t="s">
+      <c r="L236" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="M236" t="s">
+        <v>419</v>
+      </c>
+      <c r="N236" t="s">
+        <v>420</v>
+      </c>
+      <c r="O236" t="s">
+        <v>421</v>
+      </c>
+      <c r="P236" t="s">
         <v>434</v>
       </c>
-      <c r="M236" s="11" t="s">
-        <v>420</v>
-      </c>
-      <c r="N236" t="s">
-        <v>421</v>
-      </c>
-      <c r="O236" t="s">
-        <v>422</v>
-      </c>
-      <c r="P236" t="s">
+      <c r="Q236" t="s">
         <v>435</v>
-      </c>
-      <c r="Q236" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="237" spans="4:19" x14ac:dyDescent="0.25">
@@ -5079,31 +5090,31 @@
       <c r="J237" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L237" s="13"/>
-      <c r="M237" s="11" t="s">
+      <c r="L237" s="11"/>
+      <c r="M237" t="s">
+        <v>419</v>
+      </c>
+      <c r="N237" t="s">
         <v>420</v>
       </c>
-      <c r="N237" t="s">
+      <c r="O237" t="s">
         <v>421</v>
       </c>
-      <c r="O237" t="s">
-        <v>422</v>
-      </c>
       <c r="P237" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q237" t="s">
+        <v>436</v>
+      </c>
+      <c r="R237" t="s">
         <v>437</v>
-      </c>
-      <c r="R237" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="238" spans="4:19" x14ac:dyDescent="0.25">
       <c r="F238" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="L238" s="13"/>
+      <c r="L238" s="11"/>
     </row>
     <row r="239" spans="4:19" x14ac:dyDescent="0.25">
       <c r="G239" t="s">
@@ -5118,21 +5129,21 @@
       <c r="J239" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L239" s="13"/>
-      <c r="M239" s="11" t="s">
+      <c r="L239" s="11"/>
+      <c r="M239" t="s">
+        <v>419</v>
+      </c>
+      <c r="N239" t="s">
         <v>420</v>
       </c>
-      <c r="N239" t="s">
+      <c r="O239" t="s">
         <v>421</v>
       </c>
-      <c r="O239" t="s">
-        <v>422</v>
-      </c>
       <c r="P239" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q239" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="240" spans="4:19" x14ac:dyDescent="0.25">
@@ -5148,21 +5159,21 @@
       <c r="J240" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L240" s="13"/>
-      <c r="M240" s="11" t="s">
+      <c r="L240" s="11"/>
+      <c r="M240" t="s">
+        <v>419</v>
+      </c>
+      <c r="N240" t="s">
         <v>420</v>
       </c>
-      <c r="N240" t="s">
+      <c r="O240" t="s">
         <v>421</v>
       </c>
-      <c r="O240" t="s">
-        <v>422</v>
-      </c>
       <c r="P240" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q240" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="241" spans="4:18" x14ac:dyDescent="0.25">
@@ -5178,56 +5189,56 @@
       <c r="J241" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L241" s="13"/>
-      <c r="M241" s="11" t="s">
+      <c r="L241" s="11"/>
+      <c r="M241" t="s">
+        <v>419</v>
+      </c>
+      <c r="N241" t="s">
         <v>420</v>
       </c>
-      <c r="N241" t="s">
+      <c r="O241" t="s">
         <v>421</v>
       </c>
-      <c r="O241" t="s">
-        <v>422</v>
-      </c>
       <c r="P241" t="s">
+        <v>438</v>
+      </c>
+      <c r="Q241" t="s">
         <v>439</v>
-      </c>
-      <c r="Q241" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="242" spans="4:18" x14ac:dyDescent="0.25">
       <c r="F242" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="L242" s="13"/>
+      <c r="L242" s="11"/>
     </row>
     <row r="243" spans="4:18" x14ac:dyDescent="0.25">
       <c r="E243" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="L243" s="13"/>
+      <c r="L243" s="11"/>
     </row>
     <row r="244" spans="4:18" x14ac:dyDescent="0.25">
       <c r="E244" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="L244" s="14" t="s">
-        <v>441</v>
-      </c>
-      <c r="M244" s="11" t="s">
+      <c r="L244" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="M244" t="s">
+        <v>419</v>
+      </c>
+      <c r="N244" t="s">
         <v>420</v>
       </c>
-      <c r="N244" t="s">
+      <c r="O244" t="s">
         <v>421</v>
       </c>
-      <c r="O244" t="s">
-        <v>422</v>
-      </c>
       <c r="P244" t="s">
+        <v>434</v>
+      </c>
+      <c r="Q244" t="s">
         <v>435</v>
-      </c>
-      <c r="Q244" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="245" spans="4:18" x14ac:dyDescent="0.25">
@@ -5243,32 +5254,31 @@
       <c r="J245" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L245" s="13"/>
-      <c r="M245" s="11" t="s">
+      <c r="L245" s="11"/>
+      <c r="M245" t="s">
+        <v>419</v>
+      </c>
+      <c r="N245" t="s">
         <v>420</v>
       </c>
-      <c r="N245" t="s">
+      <c r="O245" t="s">
         <v>421</v>
       </c>
-      <c r="O245" t="s">
-        <v>422</v>
-      </c>
       <c r="P245" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q245" t="s">
+        <v>436</v>
+      </c>
+      <c r="R245" t="s">
         <v>437</v>
-      </c>
-      <c r="R245" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="246" spans="4:18" x14ac:dyDescent="0.25">
       <c r="F246" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="L246" s="13"/>
-      <c r="M246" s="11"/>
+      <c r="L246" s="11"/>
     </row>
     <row r="247" spans="4:18" x14ac:dyDescent="0.25">
       <c r="G247" t="s">
@@ -5283,21 +5293,21 @@
       <c r="J247" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L247" s="13"/>
-      <c r="M247" s="11" t="s">
+      <c r="L247" s="11"/>
+      <c r="M247" t="s">
+        <v>419</v>
+      </c>
+      <c r="N247" t="s">
         <v>420</v>
       </c>
-      <c r="N247" t="s">
+      <c r="O247" t="s">
         <v>421</v>
       </c>
-      <c r="O247" t="s">
-        <v>422</v>
-      </c>
       <c r="P247" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q247" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="248" spans="4:18" x14ac:dyDescent="0.25">
@@ -5313,21 +5323,21 @@
       <c r="J248" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L248" s="13"/>
-      <c r="M248" s="11" t="s">
+      <c r="L248" s="11"/>
+      <c r="M248" t="s">
+        <v>419</v>
+      </c>
+      <c r="N248" t="s">
         <v>420</v>
       </c>
-      <c r="N248" t="s">
+      <c r="O248" t="s">
         <v>421</v>
       </c>
-      <c r="O248" t="s">
-        <v>422</v>
-      </c>
       <c r="P248" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q248" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="249" spans="4:18" x14ac:dyDescent="0.25">
@@ -5343,40 +5353,40 @@
       <c r="J249" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L249" s="13"/>
-      <c r="M249" s="11" t="s">
+      <c r="L249" s="11"/>
+      <c r="M249" t="s">
+        <v>419</v>
+      </c>
+      <c r="N249" t="s">
         <v>420</v>
       </c>
-      <c r="N249" t="s">
+      <c r="O249" t="s">
         <v>421</v>
       </c>
-      <c r="O249" t="s">
-        <v>422</v>
-      </c>
       <c r="P249" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q249" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="250" spans="4:18" x14ac:dyDescent="0.25">
       <c r="F250" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="L250" s="13"/>
+      <c r="L250" s="11"/>
     </row>
     <row r="251" spans="4:18" x14ac:dyDescent="0.25">
       <c r="E251" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="L251" s="13"/>
+      <c r="L251" s="11"/>
     </row>
     <row r="252" spans="4:18" x14ac:dyDescent="0.25">
       <c r="D252" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="L252" s="13"/>
+      <c r="L252" s="11"/>
     </row>
     <row r="253" spans="4:18" x14ac:dyDescent="0.25">
       <c r="D253" s="1" t="s">
@@ -5388,7 +5398,7 @@
       <c r="J253" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L253" s="13"/>
+      <c r="L253" s="11"/>
     </row>
     <row r="254" spans="4:18" x14ac:dyDescent="0.25">
       <c r="E254" t="s">
@@ -5403,21 +5413,21 @@
       <c r="J254" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L254" s="13"/>
-      <c r="M254" s="11" t="s">
-        <v>408</v>
+      <c r="L254" s="11"/>
+      <c r="M254" t="s">
+        <v>407</v>
       </c>
       <c r="N254" t="s">
+        <v>420</v>
+      </c>
+      <c r="O254" t="s">
         <v>421</v>
       </c>
-      <c r="O254" t="s">
-        <v>422</v>
-      </c>
       <c r="P254" t="s">
+        <v>442</v>
+      </c>
+      <c r="Q254" t="s">
         <v>443</v>
-      </c>
-      <c r="Q254" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="255" spans="4:18" x14ac:dyDescent="0.25">
@@ -5433,21 +5443,21 @@
       <c r="J255" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L255" s="13"/>
-      <c r="M255" s="11" t="s">
-        <v>408</v>
+      <c r="L255" s="11"/>
+      <c r="M255" t="s">
+        <v>407</v>
       </c>
       <c r="N255" t="s">
+        <v>420</v>
+      </c>
+      <c r="O255" t="s">
         <v>421</v>
       </c>
-      <c r="O255" t="s">
-        <v>422</v>
-      </c>
       <c r="P255" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q255" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="256" spans="4:18" x14ac:dyDescent="0.25">
@@ -5463,29 +5473,28 @@
       <c r="J256" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L256" s="13"/>
-      <c r="M256" s="11" t="s">
-        <v>408</v>
+      <c r="L256" s="11"/>
+      <c r="M256" t="s">
+        <v>407</v>
       </c>
       <c r="N256" t="s">
+        <v>420</v>
+      </c>
+      <c r="O256" t="s">
         <v>421</v>
       </c>
-      <c r="O256" t="s">
-        <v>422</v>
-      </c>
       <c r="P256" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q256" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="257" spans="4:16" x14ac:dyDescent="0.25">
       <c r="E257" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L257" s="13"/>
-      <c r="M257" s="11"/>
+      <c r="L257" s="11"/>
     </row>
     <row r="258" spans="4:16" x14ac:dyDescent="0.25">
       <c r="F258" t="s">
@@ -5500,31 +5509,31 @@
       <c r="J258" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L258" s="13"/>
-      <c r="M258" s="11" t="s">
-        <v>408</v>
+      <c r="L258" s="11"/>
+      <c r="M258" t="s">
+        <v>407</v>
       </c>
       <c r="N258" t="s">
+        <v>420</v>
+      </c>
+      <c r="O258" t="s">
         <v>421</v>
       </c>
-      <c r="O258" t="s">
-        <v>422</v>
-      </c>
       <c r="P258" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="259" spans="4:16" x14ac:dyDescent="0.25">
       <c r="E259" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="L259" s="13"/>
+      <c r="L259" s="11"/>
     </row>
     <row r="260" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D260" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="L260" s="13"/>
+      <c r="L260" s="11"/>
     </row>
     <row r="261" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D261" s="1" t="s">
@@ -5536,7 +5545,7 @@
       <c r="J261" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L261" s="13"/>
+      <c r="L261" s="11"/>
     </row>
     <row r="262" spans="4:16" x14ac:dyDescent="0.25">
       <c r="E262" t="s">
@@ -5551,10 +5560,9 @@
       <c r="J262" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L262" s="13" t="s">
+      <c r="L262" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="M262" s="11"/>
     </row>
     <row r="263" spans="4:16" x14ac:dyDescent="0.25">
       <c r="E263" t="s">
@@ -5569,20 +5577,19 @@
       <c r="J263" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L263" s="13"/>
-      <c r="M263" s="11" t="s">
+      <c r="L263" s="11"/>
+      <c r="M263" t="s">
+        <v>407</v>
+      </c>
+      <c r="N263" t="s">
         <v>408</v>
-      </c>
-      <c r="N263" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="264" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D264" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="L264" s="13"/>
-      <c r="M264" s="11"/>
+      <c r="L264" s="11"/>
     </row>
     <row r="265" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D265" s="1" t="s">
@@ -5594,8 +5601,7 @@
       <c r="J265" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L265" s="13"/>
-      <c r="M265" s="11"/>
+      <c r="L265" s="11"/>
     </row>
     <row r="266" spans="4:16" x14ac:dyDescent="0.25">
       <c r="E266" t="s">
@@ -5610,12 +5616,12 @@
       <c r="J266" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L266" s="13"/>
-      <c r="M266" s="11" t="s">
-        <v>408</v>
+      <c r="L266" s="11"/>
+      <c r="M266" t="s">
+        <v>407</v>
       </c>
       <c r="N266" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="267" spans="4:16" x14ac:dyDescent="0.25">
@@ -5632,17 +5638,15 @@
         <v>32</v>
       </c>
       <c r="K267" s="9"/>
-      <c r="L267" s="13" t="s">
+      <c r="L267" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="M267" s="11"/>
     </row>
     <row r="268" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D268" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="L268" s="13"/>
-      <c r="M268" s="11"/>
+      <c r="L268" s="11"/>
     </row>
     <row r="269" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D269" s="1" t="s">
@@ -5654,8 +5658,7 @@
       <c r="J269" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L269" s="13"/>
-      <c r="M269" s="11"/>
+      <c r="L269" s="11"/>
     </row>
     <row r="270" spans="4:16" x14ac:dyDescent="0.25">
       <c r="E270" t="s">
@@ -5670,12 +5673,12 @@
       <c r="J270" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L270" s="13"/>
-      <c r="M270" s="11" t="s">
-        <v>408</v>
+      <c r="L270" s="11"/>
+      <c r="M270" t="s">
+        <v>407</v>
       </c>
       <c r="N270" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="271" spans="4:16" x14ac:dyDescent="0.25">
@@ -5692,17 +5695,15 @@
         <v>32</v>
       </c>
       <c r="K271" s="9"/>
-      <c r="L271" s="13" t="s">
+      <c r="L271" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="M271" s="11"/>
     </row>
     <row r="272" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D272" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="L272" s="13"/>
-      <c r="M272" s="11"/>
+      <c r="L272" s="11"/>
     </row>
     <row r="273" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D273" s="1" t="s">
@@ -5714,8 +5715,7 @@
       <c r="J273" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L273" s="13"/>
-      <c r="M273" s="11"/>
+      <c r="L273" s="11"/>
     </row>
     <row r="274" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E274" t="s">
@@ -5730,12 +5730,12 @@
       <c r="J274" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L274" s="13"/>
-      <c r="M274" s="11" t="s">
+      <c r="L274" s="11"/>
+      <c r="M274" t="s">
+        <v>448</v>
+      </c>
+      <c r="N274" t="s">
         <v>449</v>
-      </c>
-      <c r="N274" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="275" spans="4:15" x14ac:dyDescent="0.25">
@@ -5751,19 +5751,19 @@
       <c r="J275" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L275" s="13"/>
-      <c r="M275" s="11" t="s">
-        <v>449</v>
+      <c r="L275" s="11"/>
+      <c r="M275" t="s">
+        <v>448</v>
       </c>
       <c r="N275" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="276" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D276" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="L276" s="13"/>
+      <c r="L276" s="11"/>
     </row>
     <row r="277" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D277" s="1" t="s">
@@ -5775,17 +5775,17 @@
       <c r="J277" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L277" s="13" t="s">
+      <c r="L277" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="M277" t="s">
+        <v>407</v>
+      </c>
+      <c r="N277" t="s">
         <v>452</v>
       </c>
-      <c r="M277" s="11" t="s">
-        <v>408</v>
-      </c>
-      <c r="N277" t="s">
+      <c r="O277" t="s">
         <v>453</v>
-      </c>
-      <c r="O277" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="278" spans="4:15" x14ac:dyDescent="0.25">
@@ -5801,15 +5801,15 @@
       <c r="J278" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L278" s="13"/>
-      <c r="M278" s="11" t="s">
-        <v>408</v>
+      <c r="L278" s="11"/>
+      <c r="M278" t="s">
+        <v>407</v>
       </c>
       <c r="N278" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O278" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="279" spans="4:15" x14ac:dyDescent="0.25">
@@ -5825,15 +5825,15 @@
       <c r="J279" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L279" s="13"/>
-      <c r="M279" s="11" t="s">
-        <v>408</v>
+      <c r="L279" s="11"/>
+      <c r="M279" t="s">
+        <v>407</v>
       </c>
       <c r="N279" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O279" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="280" spans="4:15" x14ac:dyDescent="0.25">
@@ -5849,15 +5849,15 @@
       <c r="J280" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L280" s="13"/>
-      <c r="M280" s="11" t="s">
-        <v>408</v>
+      <c r="L280" s="11"/>
+      <c r="M280" t="s">
+        <v>407</v>
       </c>
       <c r="N280" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O280" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="281" spans="4:15" x14ac:dyDescent="0.25">
@@ -5873,24 +5873,24 @@
       <c r="J281" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L281" s="14" t="s">
+      <c r="L281" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="M281" t="s">
+        <v>407</v>
+      </c>
+      <c r="N281" t="s">
+        <v>452</v>
+      </c>
+      <c r="O281" t="s">
         <v>458</v>
-      </c>
-      <c r="M281" s="11" t="s">
-        <v>408</v>
-      </c>
-      <c r="N281" t="s">
-        <v>453</v>
-      </c>
-      <c r="O281" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="282" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D282" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L282" s="13"/>
+      <c r="L282" s="11"/>
     </row>
     <row r="283" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D283" s="1" t="s">
@@ -5902,7 +5902,7 @@
       <c r="J283" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L283" s="13"/>
+      <c r="L283" s="11"/>
       <c r="M283" t="s">
         <v>287</v>
       </c>
@@ -5920,12 +5920,12 @@
       <c r="J284" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L284" s="13"/>
-      <c r="M284" s="11" t="s">
+      <c r="L284" s="11"/>
+      <c r="M284" t="s">
+        <v>459</v>
+      </c>
+      <c r="N284" t="s">
         <v>460</v>
-      </c>
-      <c r="N284" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="285" spans="4:15" x14ac:dyDescent="0.25">
@@ -5941,12 +5941,12 @@
       <c r="J285" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L285" s="13"/>
-      <c r="M285" s="11" t="s">
-        <v>460</v>
+      <c r="L285" s="11"/>
+      <c r="M285" t="s">
+        <v>459</v>
       </c>
       <c r="N285" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="286" spans="4:15" x14ac:dyDescent="0.25">
@@ -5962,12 +5962,12 @@
       <c r="J286" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L286" s="13"/>
-      <c r="M286" s="11" t="s">
-        <v>460</v>
+      <c r="L286" s="11"/>
+      <c r="M286" t="s">
+        <v>459</v>
       </c>
       <c r="N286" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="287" spans="4:15" x14ac:dyDescent="0.25">
@@ -5983,25 +5983,25 @@
       <c r="J287" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L287" s="13"/>
-      <c r="M287" s="11" t="s">
-        <v>460</v>
+      <c r="L287" s="11"/>
+      <c r="M287" t="s">
+        <v>459</v>
       </c>
       <c r="N287" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="288" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D288" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="L288" s="13"/>
+      <c r="L288" s="11"/>
     </row>
     <row r="289" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D289" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="L289" s="13"/>
+      <c r="L289" s="11"/>
     </row>
     <row r="290" spans="4:13" x14ac:dyDescent="0.25">
       <c r="E290" t="s">
@@ -6016,7 +6016,7 @@
       <c r="J290" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L290" s="13"/>
+      <c r="L290" s="11"/>
       <c r="M290" t="s">
         <v>296</v>
       </c>
@@ -6025,13 +6025,13 @@
       <c r="D291" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="L291" s="13"/>
+      <c r="L291" s="11"/>
     </row>
     <row r="292" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D292" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="L292" s="13"/>
+      <c r="L292" s="11"/>
     </row>
     <row r="293" spans="4:13" x14ac:dyDescent="0.25">
       <c r="E293" t="s">
@@ -6046,7 +6046,7 @@
       <c r="J293" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L293" s="13"/>
+      <c r="L293" s="11"/>
       <c r="M293" t="s">
         <v>301</v>
       </c>
@@ -6055,7 +6055,7 @@
       <c r="D294" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="L294" s="13"/>
+      <c r="L294" s="11"/>
     </row>
     <row r="295" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D295" s="1" t="s">
@@ -6067,7 +6067,7 @@
       <c r="J295" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L295" s="13"/>
+      <c r="L295" s="11"/>
     </row>
     <row r="296" spans="4:13" x14ac:dyDescent="0.25">
       <c r="E296" t="s">
@@ -6082,7 +6082,7 @@
       <c r="J296" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L296" s="13"/>
+      <c r="L296" s="11"/>
       <c r="M296" t="s">
         <v>306</v>
       </c>
@@ -6100,7 +6100,7 @@
       <c r="J297" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L297" s="13"/>
+      <c r="L297" s="11"/>
     </row>
     <row r="298" spans="4:13" x14ac:dyDescent="0.25">
       <c r="E298" t="s">
@@ -6115,7 +6115,7 @@
       <c r="J298" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L298" s="13"/>
+      <c r="L298" s="11"/>
       <c r="M298" t="s">
         <v>311</v>
       </c>
@@ -6124,13 +6124,13 @@
       <c r="D299" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="L299" s="13"/>
+      <c r="L299" s="11"/>
     </row>
     <row r="300" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D300" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="L300" s="13"/>
+      <c r="L300" s="11"/>
     </row>
     <row r="301" spans="4:13" x14ac:dyDescent="0.25">
       <c r="E301" t="s">
@@ -6145,7 +6145,7 @@
       <c r="J301" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L301" s="13"/>
+      <c r="L301" s="11"/>
       <c r="M301" t="s">
         <v>316</v>
       </c>
@@ -6154,7 +6154,7 @@
       <c r="D302" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="L302" s="13"/>
+      <c r="L302" s="11"/>
     </row>
     <row r="303" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D303" s="1" t="s">
@@ -6166,7 +6166,7 @@
       <c r="J303" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L303" s="13"/>
+      <c r="L303" s="11"/>
     </row>
     <row r="304" spans="4:13" x14ac:dyDescent="0.25">
       <c r="E304" t="s">
@@ -6181,7 +6181,7 @@
       <c r="J304" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L304" s="13"/>
+      <c r="L304" s="11"/>
       <c r="M304" t="s">
         <v>320</v>
       </c>
@@ -6199,7 +6199,7 @@
       <c r="J305" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L305" s="13"/>
+      <c r="L305" s="11"/>
     </row>
     <row r="306" spans="4:17" x14ac:dyDescent="0.25">
       <c r="E306" t="s">
@@ -6214,7 +6214,7 @@
       <c r="J306" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L306" s="13"/>
+      <c r="L306" s="11"/>
       <c r="M306" t="s">
         <v>325</v>
       </c>
@@ -6235,7 +6235,7 @@
       <c r="K307">
         <v>1.3</v>
       </c>
-      <c r="L307" s="13"/>
+      <c r="L307" s="11"/>
       <c r="M307" t="s">
         <v>328</v>
       </c>
@@ -6244,13 +6244,13 @@
       <c r="D308" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="L308" s="13"/>
+      <c r="L308" s="11"/>
     </row>
     <row r="309" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D309" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="L309" s="13"/>
+      <c r="L309" s="11"/>
     </row>
     <row r="310" spans="4:17" x14ac:dyDescent="0.25">
       <c r="E310" t="s">
@@ -6265,12 +6265,12 @@
       <c r="J310" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L310" s="13"/>
-      <c r="M310" s="11" t="s">
+      <c r="L310" s="11"/>
+      <c r="M310" t="s">
+        <v>464</v>
+      </c>
+      <c r="N310" t="s">
         <v>465</v>
-      </c>
-      <c r="N310" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="311" spans="4:17" x14ac:dyDescent="0.25">
@@ -6286,21 +6286,21 @@
       <c r="J311" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L311" s="13"/>
-      <c r="M311" s="11" t="s">
-        <v>465</v>
+      <c r="L311" s="11"/>
+      <c r="M311" t="s">
+        <v>464</v>
       </c>
       <c r="N311" t="s">
+        <v>466</v>
+      </c>
+      <c r="O311" t="s">
         <v>467</v>
       </c>
-      <c r="O311" t="s">
+      <c r="P311" t="s">
         <v>468</v>
       </c>
-      <c r="P311" t="s">
+      <c r="Q311" t="s">
         <v>469</v>
-      </c>
-      <c r="Q311" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="312" spans="4:17" x14ac:dyDescent="0.25">
@@ -6316,14 +6316,14 @@
       <c r="J312" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L312" s="14" t="s">
-        <v>474</v>
-      </c>
-      <c r="M312" s="11" t="s">
-        <v>465</v>
+      <c r="L312" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="M312" t="s">
+        <v>464</v>
       </c>
       <c r="N312" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="313" spans="4:17" x14ac:dyDescent="0.25">
@@ -6339,14 +6339,14 @@
       <c r="J313" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L313" s="14" t="s">
-        <v>474</v>
-      </c>
-      <c r="M313" s="11" t="s">
-        <v>465</v>
+      <c r="L313" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="M313" t="s">
+        <v>464</v>
       </c>
       <c r="N313" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="314" spans="4:17" x14ac:dyDescent="0.25">
@@ -6362,7 +6362,7 @@
       <c r="J314" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L314" s="13"/>
+      <c r="L314" s="11"/>
       <c r="M314" t="s">
         <v>339</v>
       </c>
@@ -6380,12 +6380,12 @@
       <c r="J315" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L315" s="13"/>
-      <c r="M315" s="11" t="s">
-        <v>465</v>
+      <c r="L315" s="11"/>
+      <c r="M315" t="s">
+        <v>464</v>
       </c>
       <c r="N315" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="316" spans="4:17" x14ac:dyDescent="0.25">
@@ -6401,15 +6401,15 @@
       <c r="J316" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L316" s="13"/>
-      <c r="M316" s="11" t="s">
-        <v>465</v>
+      <c r="L316" s="11"/>
+      <c r="M316" t="s">
+        <v>464</v>
       </c>
       <c r="N316" t="s">
+        <v>466</v>
+      </c>
+      <c r="O316" t="s">
         <v>467</v>
-      </c>
-      <c r="O316" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="317" spans="4:17" x14ac:dyDescent="0.25">
@@ -6425,9 +6425,12 @@
       <c r="J317" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L317" s="13"/>
-      <c r="M317" t="s">
-        <v>400</v>
+      <c r="L317" s="11"/>
+      <c r="M317" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="N317" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="318" spans="4:17" x14ac:dyDescent="0.25">
@@ -6443,13 +6446,13 @@
       <c r="J318" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L318" s="13"/>
+      <c r="L318" s="11"/>
     </row>
     <row r="319" spans="4:17" x14ac:dyDescent="0.25">
       <c r="E319" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="L319" s="13"/>
+      <c r="L319" s="11"/>
     </row>
     <row r="320" spans="4:17" x14ac:dyDescent="0.25">
       <c r="F320" t="s">
@@ -6464,31 +6467,31 @@
       <c r="J320" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L320" s="13"/>
-      <c r="M320" s="11" t="s">
-        <v>465</v>
+      <c r="L320" s="11"/>
+      <c r="M320" t="s">
+        <v>464</v>
       </c>
       <c r="N320" t="s">
+        <v>466</v>
+      </c>
+      <c r="O320" t="s">
         <v>467</v>
       </c>
-      <c r="O320" t="s">
-        <v>468</v>
-      </c>
       <c r="P320" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="321" spans="5:16" x14ac:dyDescent="0.25">
       <c r="E321" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="L321" s="13"/>
+      <c r="L321" s="11"/>
     </row>
     <row r="322" spans="5:16" x14ac:dyDescent="0.25">
       <c r="E322" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="L322" s="13"/>
+      <c r="L322" s="11"/>
     </row>
     <row r="323" spans="5:16" x14ac:dyDescent="0.25">
       <c r="F323" t="s">
@@ -6503,25 +6506,25 @@
       <c r="J323" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L323" s="13"/>
-      <c r="M323" s="11" t="s">
-        <v>465</v>
+      <c r="L323" s="11"/>
+      <c r="M323" t="s">
+        <v>464</v>
       </c>
       <c r="N323" t="s">
+        <v>466</v>
+      </c>
+      <c r="O323" t="s">
         <v>467</v>
       </c>
-      <c r="O323" t="s">
-        <v>468</v>
-      </c>
       <c r="P323" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="324" spans="5:16" x14ac:dyDescent="0.25">
       <c r="E324" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="L324" s="13"/>
+      <c r="L324" s="11"/>
     </row>
     <row r="325" spans="5:16" x14ac:dyDescent="0.25">
       <c r="E325" s="1" t="s">
@@ -6533,7 +6536,7 @@
       <c r="J325" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L325" s="13"/>
+      <c r="L325" s="11"/>
     </row>
     <row r="326" spans="5:16" x14ac:dyDescent="0.25">
       <c r="F326" t="s">
@@ -6548,15 +6551,15 @@
       <c r="J326" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L326" s="13"/>
-      <c r="M326" s="11" t="s">
-        <v>465</v>
+      <c r="L326" s="11"/>
+      <c r="M326" t="s">
+        <v>464</v>
       </c>
       <c r="N326" t="s">
+        <v>476</v>
+      </c>
+      <c r="O326" t="s">
         <v>477</v>
-      </c>
-      <c r="O326" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="327" spans="5:16" x14ac:dyDescent="0.25">
@@ -6572,15 +6575,15 @@
       <c r="J327" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L327" s="13"/>
-      <c r="M327" s="11" t="s">
-        <v>465</v>
+      <c r="L327" s="11"/>
+      <c r="M327" t="s">
+        <v>464</v>
       </c>
       <c r="N327" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="O327" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="328" spans="5:16" x14ac:dyDescent="0.25">
@@ -6596,15 +6599,18 @@
       <c r="J328" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L328" s="13"/>
-      <c r="M328" s="11" t="s">
-        <v>465</v>
+      <c r="L328" s="11"/>
+      <c r="M328" t="s">
+        <v>464</v>
       </c>
       <c r="N328" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="O328" t="s">
-        <v>480</v>
+        <v>492</v>
+      </c>
+      <c r="P328" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="329" spans="5:16" x14ac:dyDescent="0.25">
@@ -6620,23 +6626,22 @@
       <c r="J329" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L329" s="13"/>
-      <c r="M329" s="11" t="s">
-        <v>465</v>
+      <c r="L329" s="11"/>
+      <c r="M329" t="s">
+        <v>464</v>
       </c>
       <c r="N329" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="O329" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="330" spans="5:16" x14ac:dyDescent="0.25">
       <c r="F330" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="L330" s="13"/>
-      <c r="M330" s="11"/>
+      <c r="L330" s="11"/>
     </row>
     <row r="331" spans="5:16" x14ac:dyDescent="0.25">
       <c r="G331" t="s">
@@ -6651,28 +6656,28 @@
       <c r="J331" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L331" s="13"/>
-      <c r="M331" s="11" t="s">
-        <v>465</v>
+      <c r="L331" s="11"/>
+      <c r="M331" t="s">
+        <v>464</v>
       </c>
       <c r="N331" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="O331" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="332" spans="5:16" x14ac:dyDescent="0.25">
       <c r="F332" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="L332" s="13"/>
+      <c r="L332" s="11"/>
     </row>
     <row r="333" spans="5:16" x14ac:dyDescent="0.25">
       <c r="E333" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="L333" s="13"/>
+      <c r="L333" s="11"/>
     </row>
     <row r="334" spans="5:16" x14ac:dyDescent="0.25">
       <c r="E334" s="1" t="s">
@@ -6684,7 +6689,7 @@
       <c r="J334" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L334" s="13"/>
+      <c r="L334" s="11"/>
     </row>
     <row r="335" spans="5:16" x14ac:dyDescent="0.25">
       <c r="F335" t="s">
@@ -6699,15 +6704,15 @@
       <c r="J335" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L335" s="13"/>
-      <c r="M335" s="11" t="s">
-        <v>465</v>
+      <c r="L335" s="11"/>
+      <c r="M335" t="s">
+        <v>464</v>
       </c>
       <c r="N335" t="s">
+        <v>466</v>
+      </c>
+      <c r="O335" t="s">
         <v>467</v>
-      </c>
-      <c r="O335" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="336" spans="5:16" x14ac:dyDescent="0.25">
@@ -6723,23 +6728,22 @@
       <c r="J336" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L336" s="13"/>
-      <c r="M336" s="11" t="s">
-        <v>465</v>
+      <c r="L336" s="11"/>
+      <c r="M336" t="s">
+        <v>464</v>
       </c>
       <c r="N336" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="O336" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="337" spans="5:17" x14ac:dyDescent="0.25">
       <c r="F337" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="L337" s="13"/>
-      <c r="M337" s="11"/>
+      <c r="L337" s="11"/>
     </row>
     <row r="338" spans="5:17" x14ac:dyDescent="0.25">
       <c r="F338" s="1"/>
@@ -6755,21 +6759,21 @@
       <c r="J338" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L338" s="13"/>
-      <c r="M338" s="11" t="s">
-        <v>465</v>
+      <c r="L338" s="11"/>
+      <c r="M338" t="s">
+        <v>464</v>
       </c>
       <c r="N338" t="s">
+        <v>466</v>
+      </c>
+      <c r="O338" t="s">
         <v>467</v>
       </c>
-      <c r="O338" t="s">
-        <v>468</v>
-      </c>
       <c r="P338" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="Q338" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="339" spans="5:17" x14ac:dyDescent="0.25">
@@ -6786,21 +6790,21 @@
       <c r="J339" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L339" s="13"/>
-      <c r="M339" s="11" t="s">
-        <v>465</v>
+      <c r="L339" s="11"/>
+      <c r="M339" t="s">
+        <v>464</v>
       </c>
       <c r="N339" t="s">
+        <v>466</v>
+      </c>
+      <c r="O339" t="s">
         <v>467</v>
       </c>
-      <c r="O339" t="s">
-        <v>468</v>
-      </c>
       <c r="P339" t="s">
+        <v>482</v>
+      </c>
+      <c r="Q339" t="s">
         <v>484</v>
-      </c>
-      <c r="Q339" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="340" spans="5:17" x14ac:dyDescent="0.25">
@@ -6817,40 +6821,40 @@
       <c r="J340" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L340" s="13"/>
-      <c r="M340" s="11" t="s">
-        <v>465</v>
+      <c r="L340" s="11"/>
+      <c r="M340" t="s">
+        <v>464</v>
       </c>
       <c r="N340" t="s">
+        <v>466</v>
+      </c>
+      <c r="O340" t="s">
         <v>467</v>
       </c>
-      <c r="O340" t="s">
-        <v>468</v>
-      </c>
       <c r="P340" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="Q340" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="341" spans="5:17" x14ac:dyDescent="0.25">
       <c r="F341" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="L341" s="13"/>
+      <c r="L341" s="11"/>
     </row>
     <row r="342" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E342" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="L342" s="13"/>
+      <c r="L342" s="11"/>
     </row>
     <row r="343" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E343" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="L343" s="13"/>
+      <c r="L343" s="11"/>
     </row>
     <row r="344" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E344" s="1"/>
@@ -6866,12 +6870,12 @@
       <c r="J344" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L344" s="13"/>
-      <c r="M344" s="11" t="s">
-        <v>465</v>
+      <c r="L344" s="11"/>
+      <c r="M344" t="s">
+        <v>464</v>
       </c>
       <c r="N344" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="345" spans="5:17" x14ac:dyDescent="0.25">
@@ -6888,21 +6892,21 @@
       <c r="J345" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L345" s="13"/>
-      <c r="M345" s="11" t="s">
-        <v>465</v>
+      <c r="L345" s="11"/>
+      <c r="M345" t="s">
+        <v>464</v>
       </c>
       <c r="N345" t="s">
+        <v>466</v>
+      </c>
+      <c r="O345" t="s">
         <v>467</v>
       </c>
-      <c r="O345" t="s">
+      <c r="P345" t="s">
         <v>468</v>
       </c>
-      <c r="P345" t="s">
-        <v>469</v>
-      </c>
       <c r="Q345" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="346" spans="5:17" x14ac:dyDescent="0.25">
@@ -6919,12 +6923,12 @@
       <c r="J346" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L346" s="13"/>
-      <c r="M346" s="11" t="s">
-        <v>465</v>
+      <c r="L346" s="11"/>
+      <c r="M346" t="s">
+        <v>464</v>
       </c>
       <c r="N346" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="347" spans="5:17" x14ac:dyDescent="0.25">
@@ -6935,12 +6939,12 @@
       <c r="H347" t="s">
         <v>385</v>
       </c>
-      <c r="L347" s="13"/>
-      <c r="M347" s="11" t="s">
-        <v>465</v>
+      <c r="L347" s="11"/>
+      <c r="M347" t="s">
+        <v>464</v>
       </c>
       <c r="N347" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="348" spans="5:17" x14ac:dyDescent="0.25">
@@ -6952,16 +6956,15 @@
         <v>387</v>
       </c>
       <c r="K348" s="9"/>
-      <c r="L348" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="M348" s="10"/>
+      <c r="L348" s="11" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="349" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E349" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="L349" s="13"/>
+      <c r="L349" s="11"/>
     </row>
     <row r="350" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E350" s="1" t="s">
@@ -6973,7 +6976,7 @@
       <c r="J350" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L350" s="13"/>
+      <c r="L350" s="11"/>
     </row>
     <row r="351" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E351" s="1"/>
@@ -6989,12 +6992,12 @@
       <c r="J351" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L351" s="13"/>
-      <c r="M351" s="11" t="s">
+      <c r="L351" s="11"/>
+      <c r="M351" t="s">
+        <v>459</v>
+      </c>
+      <c r="N351" t="s">
         <v>460</v>
-      </c>
-      <c r="N351" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="352" spans="5:17" x14ac:dyDescent="0.25">
@@ -7011,12 +7014,12 @@
       <c r="J352" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L352" s="13"/>
-      <c r="M352" s="11" t="s">
-        <v>460</v>
+      <c r="L352" s="11"/>
+      <c r="M352" t="s">
+        <v>459</v>
       </c>
       <c r="N352" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.25">
@@ -7033,12 +7036,12 @@
       <c r="J353" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L353" s="13"/>
-      <c r="M353" s="11" t="s">
-        <v>460</v>
+      <c r="L353" s="11"/>
+      <c r="M353" t="s">
+        <v>459</v>
       </c>
       <c r="N353" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.25">
@@ -7055,25 +7058,25 @@
       <c r="J354" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L354" s="13"/>
-      <c r="M354" s="11" t="s">
-        <v>460</v>
+      <c r="L354" s="11"/>
+      <c r="M354" t="s">
+        <v>459</v>
       </c>
       <c r="N354" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E355" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="L355" s="13"/>
+      <c r="L355" s="11"/>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E356" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="L356" s="13"/>
+      <c r="L356" s="11"/>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E357" s="1"/>
@@ -7089,12 +7092,12 @@
       <c r="J357" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L357" s="16"/>
-      <c r="M357" s="11" t="s">
-        <v>465</v>
+      <c r="L357" s="14"/>
+      <c r="M357" t="s">
+        <v>464</v>
       </c>
       <c r="N357" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.25">
@@ -7102,32 +7105,32 @@
         <v>392</v>
       </c>
       <c r="F358" s="1"/>
-      <c r="L358" s="13"/>
+      <c r="L358" s="11"/>
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D359" s="1" t="s">
         <v>393</v>
       </c>
       <c r="E359" s="1"/>
-      <c r="L359" s="13"/>
+      <c r="L359" s="11"/>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C360" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L360" s="13"/>
+      <c r="L360" s="11"/>
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B361" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L361" s="13"/>
+      <c r="L361" s="11"/>
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="L362" s="13"/>
+      <c r="L362" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:M2" xr:uid="{AF1D5207-AAE4-40A7-897B-0A14B8C76F5C}">
@@ -7153,6 +7156,9 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId9"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Aptos"&amp;10&amp;K000000 Unrestricted&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -7163,6 +7169,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003BD9F489D8A3CB4CB4A9ED284A3FCA6E" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9f6f1c074eaefb361d518fe95996ab9d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0298a7ca-5e45-41ce-82dd-77fd4fe196fc" xmlns:ns3="cd402ee1-b2ab-4875-af71-19f72223aa0b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9118947706f37de36bda36ecf87158af" ns2:_="" ns3:_="">
     <xsd:import namespace="0298a7ca-5e45-41ce-82dd-77fd4fe196fc"/>
@@ -7385,15 +7400,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B130662-8EB9-4540-BC8F-0D1232647753}">
   <ds:schemaRefs>
@@ -7412,6 +7418,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F75F45A3-32E6-4084-931F-E62125045A6C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AB3A138-2C3A-40ED-BC06-2CB1DD202F66}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7430,10 +7444,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F75F45A3-32E6-4084-931F-E62125045A6C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{44ae014c-8170-484b-8a8e-3a6b842e2604}" enabled="1" method="Standard" siteId="{ad221784-72a8-4263-ac86-0ccc6b152cd8}" removed="0"/>
+</clbl:labelList>
 </file>